--- a/TP3/ocupados_X_2025_MM_describe.xlsx
+++ b/TP3/ocupados_X_2025_MM_describe.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2197,17 +2197,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cat_ocup_cat_Obrero o empleado</t>
+          <t>informal_2024_Informal</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>7203</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.1445</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4489</v>
+        <v>0.3516</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2216,291 +2216,12 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>cat_ocup_cat_Patron</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>7203</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.0364</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.1872</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>cat_ocup_cat_Trab. familiar sin remuneracion</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>7203</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.0471</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>comprobante_sal_cat_Factura</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>7203</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.0278</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0.1643</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>comprobante_sal_cat_Nada</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>7203</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.1824</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0.3862</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>comprobante_sal_cat_Recibo_nosello</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>7203</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0.1199</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>comprobante_sal_cat_Recibo_sello</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>7203</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.4915</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>alcance_recibo_cat_Totalidad</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>7203</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.4738</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0.4993</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>parte_sueldo_cat_Totalidad</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>7203</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0.0047</v>
-      </c>
-      <c r="D66" t="n">
-        <v>0.06850000000000001</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>informal_2024_Informal</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>7203</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.1445</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0.3516</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
         <v>1</v>
       </c>
     </row>
